--- a/etc/fakeG.xlsx
+++ b/etc/fakeG.xlsx
@@ -5,19 +5,19 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WenJinMincho\etc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Repositories\WenJinMincho\etc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D8D26F3-1AA7-4047-9817-620B271A4B94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1D9E3B7-4913-45E7-8913-ACF5594AFD87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{922536F4-34CD-4474-AF0D-9DA1B0E2870D}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{922536F4-34CD-4474-AF0D-9DA1B0E2870D}"/>
   </bookViews>
   <sheets>
     <sheet name="说明 | Readme" sheetId="3" r:id="rId1"/>
     <sheet name="假想G源 | Pseudo G Source" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'假想G源 | Pseudo G Source'!$A$1:$N$555</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'假想G源 | Pseudo G Source'!$A$1:$O$572</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2779" uniqueCount="641">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2813" uniqueCount="651">
   <si>
     <t>uniSrc</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -2080,6 +2080,41 @@
       </rPr>
       <t>6450915722621</t>
     </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MY1L</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>绵饴字集（主表部分）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.maoken.com/eyes/business/27905.html</t>
+  </si>
+  <si>
+    <t>MY1L Characters Set (main table part)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>U+20E73</t>
+  </si>
+  <si>
+    <t>U+3127B</t>
+  </si>
+  <si>
+    <t>U+3128A</t>
+  </si>
+  <si>
+    <t>U+31E40</t>
+  </si>
+  <si>
+    <t>U+3277B</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>UK</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2202,11 +2237,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2559,7 +2594,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{722FFF3B-589D-40BA-9E5A-52450AACCCCD}">
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="16.06640625" customWidth="1"/>
@@ -2722,85 +2757,99 @@
       <c r="C16" t="s">
         <v>613</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D16" s="5" t="s">
         <v>640</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
+        <v>641</v>
+      </c>
+      <c r="B17" t="s">
+        <v>642</v>
+      </c>
+      <c r="C17" t="s">
+        <v>644</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A18" t="s">
         <v>561</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B18" t="s">
         <v>562</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C18" t="s">
         <v>618</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="20.25" x14ac:dyDescent="0.4">
-      <c r="A19" s="3" t="s">
+    <row r="20" spans="1:7" ht="20.25" x14ac:dyDescent="0.4">
+      <c r="A20" s="3" t="s">
         <v>567</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="41.2" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="5" t="s">
+    <row r="21" spans="1:7" ht="41.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="6" t="s">
         <v>603</v>
       </c>
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A22" t="s">
-        <v>574</v>
-      </c>
-      <c r="B22" t="s">
-        <v>576</v>
-      </c>
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="4"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B23" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
+        <v>575</v>
+      </c>
+      <c r="B24" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A25" t="s">
         <v>599</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B25" t="s">
         <v>568</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="B25" t="s">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="B26" t="s">
         <v>569</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A26" t="s">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A27" t="s">
         <v>570</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B27" t="s">
         <v>571</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="16.5" x14ac:dyDescent="0.4">
-      <c r="A27" t="s">
+    <row r="28" spans="1:7" ht="16.5" x14ac:dyDescent="0.4">
+      <c r="A28" t="s">
         <v>572</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B28" t="s">
         <v>573</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
@@ -2812,10 +2861,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00E93854-CA35-4A6A-8541-6A17C44224E7}">
-  <dimension ref="A1:N567"/>
+  <dimension ref="A1:O572"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>535</v>
       </c>
@@ -2856,10 +2905,13 @@
         <v>611</v>
       </c>
       <c r="N1" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="O1" s="1" t="s">
         <v>561</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -2870,7 +2922,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -2881,7 +2933,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2892,7 +2944,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -2903,7 +2955,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -2914,7 +2966,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -2925,7 +2977,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -2936,7 +2988,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -2947,7 +2999,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -2958,7 +3010,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -2969,7 +3021,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -2980,7 +3032,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -2991,7 +3043,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -3002,7 +3054,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -3013,7 +3065,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -7424,7 +7476,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="417" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="417" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A417" t="s">
         <v>416</v>
       </c>
@@ -7435,7 +7487,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="418" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="418" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A418" t="s">
         <v>584</v>
       </c>
@@ -7473,7 +7525,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="419" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="419" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A419" t="s">
         <v>417</v>
       </c>
@@ -7508,7 +7560,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="420" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="420" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A420" t="s">
         <v>418</v>
       </c>
@@ -7543,7 +7595,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="421" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="421" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A421" t="s">
         <v>419</v>
       </c>
@@ -7578,7 +7630,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="422" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="422" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A422" t="s">
         <v>420</v>
       </c>
@@ -7612,11 +7664,11 @@
       <c r="M422" t="s">
         <v>579</v>
       </c>
-      <c r="N422" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="423" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="O422" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="423" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A423" t="s">
         <v>421</v>
       </c>
@@ -7651,7 +7703,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="424" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="424" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A424" t="s">
         <v>422</v>
       </c>
@@ -7686,7 +7738,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="425" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="425" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A425" t="s">
         <v>423</v>
       </c>
@@ -7721,7 +7773,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="426" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="426" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A426" t="s">
         <v>424</v>
       </c>
@@ -7756,7 +7808,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="427" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="427" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A427" t="s">
         <v>425</v>
       </c>
@@ -7791,7 +7843,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="428" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="428" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A428" t="s">
         <v>426</v>
       </c>
@@ -7826,7 +7878,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="429" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="429" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A429" t="s">
         <v>427</v>
       </c>
@@ -7861,9 +7913,9 @@
         <v>579</v>
       </c>
     </row>
-    <row r="430" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="430" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A430" t="s">
-        <v>428</v>
+        <v>645</v>
       </c>
       <c r="B430" t="s">
         <v>540</v>
@@ -7887,7 +7939,7 @@
         <v>579</v>
       </c>
       <c r="J430" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="K430" t="s">
         <v>579</v>
@@ -7895,10 +7947,13 @@
       <c r="M430" t="s">
         <v>579</v>
       </c>
-    </row>
-    <row r="431" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="N430" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="431" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A431" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B431" t="s">
         <v>540</v>
@@ -7931,9 +7986,9 @@
         <v>579</v>
       </c>
     </row>
-    <row r="432" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="432" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A432" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B432" t="s">
         <v>540</v>
@@ -7966,9 +8021,9 @@
         <v>579</v>
       </c>
     </row>
-    <row r="433" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="433" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A433" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B433" t="s">
         <v>540</v>
@@ -8001,9 +8056,9 @@
         <v>579</v>
       </c>
     </row>
-    <row r="434" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="434" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A434" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B434" t="s">
         <v>540</v>
@@ -8036,9 +8091,9 @@
         <v>579</v>
       </c>
     </row>
-    <row r="435" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="435" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A435" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B435" t="s">
         <v>540</v>
@@ -8071,9 +8126,9 @@
         <v>579</v>
       </c>
     </row>
-    <row r="436" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="436" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A436" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B436" t="s">
         <v>540</v>
@@ -8106,9 +8161,9 @@
         <v>579</v>
       </c>
     </row>
-    <row r="437" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="437" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A437" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B437" t="s">
         <v>540</v>
@@ -8141,9 +8196,9 @@
         <v>579</v>
       </c>
     </row>
-    <row r="438" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="438" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A438" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B438" t="s">
         <v>540</v>
@@ -8176,9 +8231,9 @@
         <v>579</v>
       </c>
     </row>
-    <row r="439" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="439" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A439" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B439" t="s">
         <v>540</v>
@@ -8211,9 +8266,9 @@
         <v>579</v>
       </c>
     </row>
-    <row r="440" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="440" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A440" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B440" t="s">
         <v>540</v>
@@ -8246,9 +8301,9 @@
         <v>579</v>
       </c>
     </row>
-    <row r="441" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="441" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A441" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B441" t="s">
         <v>540</v>
@@ -8281,9 +8336,9 @@
         <v>579</v>
       </c>
     </row>
-    <row r="442" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="442" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A442" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B442" t="s">
         <v>540</v>
@@ -8316,9 +8371,9 @@
         <v>579</v>
       </c>
     </row>
-    <row r="443" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="443" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A443" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B443" t="s">
         <v>540</v>
@@ -8351,9 +8406,9 @@
         <v>579</v>
       </c>
     </row>
-    <row r="444" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="444" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A444" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B444" t="s">
         <v>540</v>
@@ -8386,9 +8441,9 @@
         <v>579</v>
       </c>
     </row>
-    <row r="445" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="445" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A445" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B445" t="s">
         <v>540</v>
@@ -8400,79 +8455,79 @@
         <v>579</v>
       </c>
       <c r="F445" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="G445" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H445" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="I445" t="s">
         <v>579</v>
       </c>
       <c r="J445" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="K445" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="M445" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="446" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="446" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A446" t="s">
+        <v>443</v>
+      </c>
+      <c r="B446" t="s">
+        <v>540</v>
+      </c>
+      <c r="D446" t="s">
+        <v>579</v>
+      </c>
+      <c r="E446" t="s">
+        <v>579</v>
+      </c>
+      <c r="F446" t="s">
+        <v>578</v>
+      </c>
+      <c r="G446" t="s">
+        <v>578</v>
+      </c>
+      <c r="H446" t="s">
+        <v>578</v>
+      </c>
+      <c r="I446" t="s">
+        <v>579</v>
+      </c>
+      <c r="J446" t="s">
+        <v>579</v>
+      </c>
+      <c r="K446" t="s">
+        <v>578</v>
+      </c>
+      <c r="M446" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="447" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A447" t="s">
         <v>585</v>
       </c>
-      <c r="B446" t="s">
+      <c r="B447" t="s">
         <v>539</v>
       </c>
-      <c r="M446" t="s">
-        <v>579</v>
-      </c>
-      <c r="N446" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="447" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A447" t="s">
+      <c r="M447" t="s">
+        <v>579</v>
+      </c>
+      <c r="O447" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="448" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A448" t="s">
         <v>444</v>
-      </c>
-      <c r="B447" t="s">
-        <v>540</v>
-      </c>
-      <c r="D447" t="s">
-        <v>579</v>
-      </c>
-      <c r="E447" t="s">
-        <v>579</v>
-      </c>
-      <c r="F447" t="s">
-        <v>579</v>
-      </c>
-      <c r="G447" t="s">
-        <v>579</v>
-      </c>
-      <c r="H447" t="s">
-        <v>579</v>
-      </c>
-      <c r="I447" t="s">
-        <v>579</v>
-      </c>
-      <c r="J447" t="s">
-        <v>578</v>
-      </c>
-      <c r="K447" t="s">
-        <v>579</v>
-      </c>
-      <c r="M447" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="448" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A448" t="s">
-        <v>445</v>
       </c>
       <c r="B448" t="s">
         <v>540</v>
@@ -8505,58 +8560,58 @@
         <v>579</v>
       </c>
     </row>
-    <row r="449" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="449" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A449" t="s">
+        <v>445</v>
+      </c>
+      <c r="B449" t="s">
+        <v>540</v>
+      </c>
+      <c r="D449" t="s">
+        <v>579</v>
+      </c>
+      <c r="E449" t="s">
+        <v>579</v>
+      </c>
+      <c r="F449" t="s">
+        <v>579</v>
+      </c>
+      <c r="G449" t="s">
+        <v>579</v>
+      </c>
+      <c r="H449" t="s">
+        <v>579</v>
+      </c>
+      <c r="I449" t="s">
+        <v>579</v>
+      </c>
+      <c r="J449" t="s">
+        <v>578</v>
+      </c>
+      <c r="K449" t="s">
+        <v>579</v>
+      </c>
+      <c r="M449" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="450" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A450" t="s">
         <v>586</v>
       </c>
-      <c r="B449" t="s">
+      <c r="B450" t="s">
         <v>539</v>
       </c>
-      <c r="L449" t="s">
-        <v>578</v>
-      </c>
-      <c r="M449" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="450" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A450" t="s">
+      <c r="L450" t="s">
+        <v>578</v>
+      </c>
+      <c r="M450" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="451" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A451" t="s">
         <v>446</v>
-      </c>
-      <c r="B450" t="s">
-        <v>540</v>
-      </c>
-      <c r="D450" t="s">
-        <v>579</v>
-      </c>
-      <c r="E450" t="s">
-        <v>579</v>
-      </c>
-      <c r="F450" t="s">
-        <v>579</v>
-      </c>
-      <c r="G450" t="s">
-        <v>579</v>
-      </c>
-      <c r="H450" t="s">
-        <v>579</v>
-      </c>
-      <c r="I450" t="s">
-        <v>579</v>
-      </c>
-      <c r="J450" t="s">
-        <v>578</v>
-      </c>
-      <c r="K450" t="s">
-        <v>579</v>
-      </c>
-      <c r="M450" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="451" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A451" t="s">
-        <v>447</v>
       </c>
       <c r="B451" t="s">
         <v>540</v>
@@ -8589,9 +8644,9 @@
         <v>579</v>
       </c>
     </row>
-    <row r="452" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="452" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A452" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B452" t="s">
         <v>540</v>
@@ -8624,9 +8679,9 @@
         <v>579</v>
       </c>
     </row>
-    <row r="453" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="453" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A453" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B453" t="s">
         <v>540</v>
@@ -8659,9 +8714,9 @@
         <v>579</v>
       </c>
     </row>
-    <row r="454" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="454" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A454" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B454" t="s">
         <v>540</v>
@@ -8694,117 +8749,117 @@
         <v>579</v>
       </c>
     </row>
-    <row r="455" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="455" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A455" t="s">
+        <v>450</v>
+      </c>
+      <c r="B455" t="s">
+        <v>540</v>
+      </c>
+      <c r="D455" t="s">
+        <v>579</v>
+      </c>
+      <c r="E455" t="s">
+        <v>579</v>
+      </c>
+      <c r="F455" t="s">
+        <v>579</v>
+      </c>
+      <c r="G455" t="s">
+        <v>579</v>
+      </c>
+      <c r="H455" t="s">
+        <v>579</v>
+      </c>
+      <c r="I455" t="s">
+        <v>579</v>
+      </c>
+      <c r="J455" t="s">
+        <v>578</v>
+      </c>
+      <c r="K455" t="s">
+        <v>579</v>
+      </c>
+      <c r="M455" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="456" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A456" t="s">
         <v>451</v>
       </c>
-      <c r="B455" t="s">
+      <c r="B456" t="s">
         <v>539</v>
       </c>
-      <c r="D455" t="s">
-        <v>579</v>
-      </c>
-      <c r="E455" t="s">
-        <v>579</v>
-      </c>
-      <c r="F455" t="s">
-        <v>578</v>
-      </c>
-      <c r="G455" t="s">
-        <v>578</v>
-      </c>
-      <c r="H455" t="s">
-        <v>578</v>
-      </c>
-      <c r="I455" t="s">
-        <v>579</v>
-      </c>
-      <c r="J455" t="s">
-        <v>578</v>
-      </c>
-      <c r="K455" t="s">
-        <v>579</v>
-      </c>
-      <c r="M455" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="456" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A456" t="s">
+      <c r="D456" t="s">
+        <v>579</v>
+      </c>
+      <c r="E456" t="s">
+        <v>579</v>
+      </c>
+      <c r="F456" t="s">
+        <v>578</v>
+      </c>
+      <c r="G456" t="s">
+        <v>578</v>
+      </c>
+      <c r="H456" t="s">
+        <v>578</v>
+      </c>
+      <c r="I456" t="s">
+        <v>579</v>
+      </c>
+      <c r="J456" t="s">
+        <v>578</v>
+      </c>
+      <c r="K456" t="s">
+        <v>579</v>
+      </c>
+      <c r="M456" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="457" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A457" t="s">
         <v>452</v>
       </c>
-      <c r="B456" t="s">
+      <c r="B457" t="s">
         <v>542</v>
       </c>
-      <c r="D456" t="s">
-        <v>579</v>
-      </c>
-      <c r="E456" t="s">
-        <v>579</v>
-      </c>
-      <c r="F456" t="s">
-        <v>579</v>
-      </c>
-      <c r="G456" t="s">
-        <v>579</v>
-      </c>
-      <c r="H456" t="s">
-        <v>579</v>
-      </c>
-      <c r="I456" t="s">
-        <v>579</v>
-      </c>
-      <c r="J456" t="s">
-        <v>579</v>
-      </c>
-      <c r="K456" t="s">
-        <v>579</v>
-      </c>
-      <c r="M456" t="s">
-        <v>579</v>
-      </c>
-      <c r="N456" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="457" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A457" t="s">
+      <c r="D457" t="s">
+        <v>579</v>
+      </c>
+      <c r="E457" t="s">
+        <v>579</v>
+      </c>
+      <c r="F457" t="s">
+        <v>579</v>
+      </c>
+      <c r="G457" t="s">
+        <v>579</v>
+      </c>
+      <c r="H457" t="s">
+        <v>579</v>
+      </c>
+      <c r="I457" t="s">
+        <v>579</v>
+      </c>
+      <c r="J457" t="s">
+        <v>579</v>
+      </c>
+      <c r="K457" t="s">
+        <v>579</v>
+      </c>
+      <c r="M457" t="s">
+        <v>579</v>
+      </c>
+      <c r="O457" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="458" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A458" t="s">
         <v>453</v>
-      </c>
-      <c r="B457" t="s">
-        <v>540</v>
-      </c>
-      <c r="D457" t="s">
-        <v>579</v>
-      </c>
-      <c r="E457" t="s">
-        <v>579</v>
-      </c>
-      <c r="F457" t="s">
-        <v>579</v>
-      </c>
-      <c r="G457" t="s">
-        <v>579</v>
-      </c>
-      <c r="H457" t="s">
-        <v>579</v>
-      </c>
-      <c r="I457" t="s">
-        <v>579</v>
-      </c>
-      <c r="J457" t="s">
-        <v>578</v>
-      </c>
-      <c r="K457" t="s">
-        <v>579</v>
-      </c>
-      <c r="M457" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="458" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A458" t="s">
-        <v>454</v>
       </c>
       <c r="B458" t="s">
         <v>540</v>
@@ -8837,114 +8892,117 @@
         <v>579</v>
       </c>
     </row>
-    <row r="459" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="459" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A459" t="s">
+        <v>454</v>
+      </c>
+      <c r="B459" t="s">
+        <v>540</v>
+      </c>
+      <c r="D459" t="s">
+        <v>579</v>
+      </c>
+      <c r="E459" t="s">
+        <v>579</v>
+      </c>
+      <c r="F459" t="s">
+        <v>579</v>
+      </c>
+      <c r="G459" t="s">
+        <v>579</v>
+      </c>
+      <c r="H459" t="s">
+        <v>579</v>
+      </c>
+      <c r="I459" t="s">
+        <v>579</v>
+      </c>
+      <c r="J459" t="s">
+        <v>578</v>
+      </c>
+      <c r="K459" t="s">
+        <v>579</v>
+      </c>
+      <c r="M459" t="s">
+        <v>579</v>
+      </c>
+      <c r="N459" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="460" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A460" t="s">
         <v>619</v>
       </c>
-      <c r="B459" t="s">
+      <c r="B460" t="s">
         <v>638</v>
       </c>
-      <c r="D459" t="s">
-        <v>579</v>
-      </c>
-      <c r="E459" t="s">
-        <v>579</v>
-      </c>
-      <c r="F459" t="s">
-        <v>579</v>
-      </c>
-      <c r="G459" t="s">
-        <v>579</v>
-      </c>
-      <c r="H459" t="s">
-        <v>579</v>
-      </c>
-      <c r="I459" t="s">
-        <v>579</v>
-      </c>
-      <c r="J459" t="s">
-        <v>579</v>
-      </c>
-      <c r="K459" t="s">
-        <v>579</v>
-      </c>
-      <c r="M459" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="460" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A460" t="s">
+      <c r="D460" t="s">
+        <v>579</v>
+      </c>
+      <c r="E460" t="s">
+        <v>579</v>
+      </c>
+      <c r="F460" t="s">
+        <v>579</v>
+      </c>
+      <c r="G460" t="s">
+        <v>579</v>
+      </c>
+      <c r="H460" t="s">
+        <v>579</v>
+      </c>
+      <c r="I460" t="s">
+        <v>579</v>
+      </c>
+      <c r="J460" t="s">
+        <v>579</v>
+      </c>
+      <c r="K460" t="s">
+        <v>579</v>
+      </c>
+      <c r="M460" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="461" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A461" t="s">
         <v>455</v>
       </c>
-      <c r="B460" t="s">
+      <c r="B461" t="s">
         <v>537</v>
       </c>
-      <c r="D460" t="s">
-        <v>579</v>
-      </c>
-      <c r="E460" t="s">
-        <v>579</v>
-      </c>
-      <c r="F460" t="s">
-        <v>579</v>
-      </c>
-      <c r="G460" t="s">
-        <v>579</v>
-      </c>
-      <c r="H460" t="s">
-        <v>579</v>
-      </c>
-      <c r="I460" t="s">
-        <v>579</v>
-      </c>
-      <c r="J460" t="s">
-        <v>578</v>
-      </c>
-      <c r="K460" t="s">
-        <v>579</v>
-      </c>
-      <c r="M460" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="461" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A461" t="s">
+      <c r="D461" t="s">
+        <v>579</v>
+      </c>
+      <c r="E461" t="s">
+        <v>579</v>
+      </c>
+      <c r="F461" t="s">
+        <v>579</v>
+      </c>
+      <c r="G461" t="s">
+        <v>579</v>
+      </c>
+      <c r="H461" t="s">
+        <v>579</v>
+      </c>
+      <c r="I461" t="s">
+        <v>579</v>
+      </c>
+      <c r="J461" t="s">
+        <v>578</v>
+      </c>
+      <c r="K461" t="s">
+        <v>579</v>
+      </c>
+      <c r="M461" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="462" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A462" t="s">
         <v>456</v>
-      </c>
-      <c r="B461" t="s">
-        <v>540</v>
-      </c>
-      <c r="D461" t="s">
-        <v>579</v>
-      </c>
-      <c r="E461" t="s">
-        <v>579</v>
-      </c>
-      <c r="F461" t="s">
-        <v>579</v>
-      </c>
-      <c r="G461" t="s">
-        <v>579</v>
-      </c>
-      <c r="H461" t="s">
-        <v>579</v>
-      </c>
-      <c r="I461" t="s">
-        <v>579</v>
-      </c>
-      <c r="J461" t="s">
-        <v>578</v>
-      </c>
-      <c r="K461" t="s">
-        <v>579</v>
-      </c>
-      <c r="M461" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="462" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A462" t="s">
-        <v>457</v>
       </c>
       <c r="B462" t="s">
         <v>540</v>
@@ -8977,9 +9035,9 @@
         <v>579</v>
       </c>
     </row>
-    <row r="463" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="463" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A463" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B463" t="s">
         <v>540</v>
@@ -8988,7 +9046,7 @@
         <v>579</v>
       </c>
       <c r="E463" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="F463" t="s">
         <v>579</v>
@@ -9000,10 +9058,10 @@
         <v>579</v>
       </c>
       <c r="I463" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="J463" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="K463" t="s">
         <v>579</v>
@@ -9012,36 +9070,36 @@
         <v>579</v>
       </c>
     </row>
-    <row r="464" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="464" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A464" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B464" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="D464" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="E464" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="F464" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="G464" t="s">
         <v>579</v>
       </c>
       <c r="H464" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="I464" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="J464" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="K464" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="M464" t="s">
         <v>579</v>
@@ -9049,31 +9107,34 @@
     </row>
     <row r="465" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A465" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B465" t="s">
-        <v>595</v>
+        <v>542</v>
       </c>
       <c r="D465" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="E465" t="s">
         <v>579</v>
       </c>
       <c r="F465" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="G465" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H465" t="s">
         <v>578</v>
       </c>
+      <c r="I465" t="s">
+        <v>579</v>
+      </c>
       <c r="J465" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="K465" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="M465" t="s">
         <v>579</v>
@@ -9081,10 +9142,10 @@
     </row>
     <row r="466" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A466" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B466" t="s">
-        <v>539</v>
+        <v>595</v>
       </c>
       <c r="D466" t="s">
         <v>579</v>
@@ -9093,7 +9154,7 @@
         <v>579</v>
       </c>
       <c r="F466" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="G466" t="s">
         <v>578</v>
@@ -9101,14 +9162,11 @@
       <c r="H466" t="s">
         <v>578</v>
       </c>
-      <c r="I466" t="s">
-        <v>579</v>
-      </c>
       <c r="J466" t="s">
         <v>579</v>
       </c>
       <c r="K466" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="M466" t="s">
         <v>579</v>
@@ -9116,10 +9174,10 @@
     </row>
     <row r="467" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A467" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B467" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D467" t="s">
         <v>579</v>
@@ -9128,22 +9186,22 @@
         <v>579</v>
       </c>
       <c r="F467" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="G467" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H467" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="I467" t="s">
         <v>579</v>
       </c>
       <c r="J467" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="K467" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="M467" t="s">
         <v>579</v>
@@ -9151,7 +9209,7 @@
     </row>
     <row r="468" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A468" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B468" t="s">
         <v>540</v>
@@ -9186,7 +9244,7 @@
     </row>
     <row r="469" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A469" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B469" t="s">
         <v>540</v>
@@ -9221,7 +9279,7 @@
     </row>
     <row r="470" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A470" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B470" t="s">
         <v>540</v>
@@ -9256,7 +9314,7 @@
     </row>
     <row r="471" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A471" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B471" t="s">
         <v>540</v>
@@ -9291,7 +9349,7 @@
     </row>
     <row r="472" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A472" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B472" t="s">
         <v>540</v>
@@ -9326,10 +9384,10 @@
     </row>
     <row r="473" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A473" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B473" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="D473" t="s">
         <v>579</v>
@@ -9361,10 +9419,10 @@
     </row>
     <row r="474" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A474" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B474" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="D474" t="s">
         <v>579</v>
@@ -9373,22 +9431,22 @@
         <v>579</v>
       </c>
       <c r="F474" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="G474" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H474" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="I474" t="s">
         <v>579</v>
       </c>
       <c r="J474" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="K474" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="M474" t="s">
         <v>579</v>
@@ -9396,10 +9454,10 @@
     </row>
     <row r="475" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A475" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B475" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D475" t="s">
         <v>579</v>
@@ -9408,22 +9466,22 @@
         <v>579</v>
       </c>
       <c r="F475" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="G475" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H475" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="I475" t="s">
         <v>579</v>
       </c>
       <c r="J475" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="K475" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="M475" t="s">
         <v>579</v>
@@ -9431,7 +9489,7 @@
     </row>
     <row r="476" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A476" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B476" t="s">
         <v>540</v>
@@ -9466,7 +9524,7 @@
     </row>
     <row r="477" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A477" t="s">
-        <v>620</v>
+        <v>471</v>
       </c>
       <c r="B477" t="s">
         <v>540</v>
@@ -9490,21 +9548,21 @@
         <v>579</v>
       </c>
       <c r="J477" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="K477" t="s">
         <v>579</v>
       </c>
       <c r="M477" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="478" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A478" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B478" t="s">
-        <v>638</v>
+        <v>540</v>
       </c>
       <c r="D478" t="s">
         <v>579</v>
@@ -9536,10 +9594,10 @@
     </row>
     <row r="479" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A479" t="s">
-        <v>472</v>
+        <v>621</v>
       </c>
       <c r="B479" t="s">
-        <v>540</v>
+        <v>638</v>
       </c>
       <c r="D479" t="s">
         <v>579</v>
@@ -9560,53 +9618,53 @@
         <v>579</v>
       </c>
       <c r="J479" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="K479" t="s">
         <v>579</v>
       </c>
       <c r="M479" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="480" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A480" t="s">
+        <v>472</v>
+      </c>
+      <c r="B480" t="s">
+        <v>540</v>
+      </c>
+      <c r="D480" t="s">
+        <v>579</v>
+      </c>
+      <c r="E480" t="s">
+        <v>579</v>
+      </c>
+      <c r="F480" t="s">
+        <v>579</v>
+      </c>
+      <c r="G480" t="s">
+        <v>579</v>
+      </c>
+      <c r="H480" t="s">
+        <v>579</v>
+      </c>
+      <c r="I480" t="s">
+        <v>579</v>
+      </c>
+      <c r="J480" t="s">
+        <v>578</v>
+      </c>
+      <c r="K480" t="s">
+        <v>579</v>
+      </c>
+      <c r="M480" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="481" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A481" t="s">
         <v>622</v>
-      </c>
-      <c r="B480" t="s">
-        <v>638</v>
-      </c>
-      <c r="D480" t="s">
-        <v>579</v>
-      </c>
-      <c r="E480" t="s">
-        <v>579</v>
-      </c>
-      <c r="F480" t="s">
-        <v>579</v>
-      </c>
-      <c r="G480" t="s">
-        <v>579</v>
-      </c>
-      <c r="H480" t="s">
-        <v>579</v>
-      </c>
-      <c r="I480" t="s">
-        <v>579</v>
-      </c>
-      <c r="J480" t="s">
-        <v>579</v>
-      </c>
-      <c r="K480" t="s">
-        <v>579</v>
-      </c>
-      <c r="M480" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="481" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A481" t="s">
-        <v>623</v>
       </c>
       <c r="B481" t="s">
         <v>638</v>
@@ -9639,104 +9697,125 @@
         <v>578</v>
       </c>
     </row>
-    <row r="482" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="482" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A482" t="s">
+        <v>623</v>
+      </c>
+      <c r="B482" t="s">
+        <v>638</v>
+      </c>
+      <c r="D482" t="s">
+        <v>579</v>
+      </c>
+      <c r="E482" t="s">
+        <v>579</v>
+      </c>
+      <c r="F482" t="s">
+        <v>579</v>
+      </c>
+      <c r="G482" t="s">
+        <v>579</v>
+      </c>
+      <c r="H482" t="s">
+        <v>579</v>
+      </c>
+      <c r="I482" t="s">
+        <v>579</v>
+      </c>
+      <c r="J482" t="s">
+        <v>579</v>
+      </c>
+      <c r="K482" t="s">
+        <v>579</v>
+      </c>
+      <c r="M482" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="483" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A483" t="s">
         <v>473</v>
       </c>
-      <c r="B482" t="s">
+      <c r="B483" t="s">
         <v>542</v>
       </c>
-      <c r="H482" t="s">
-        <v>578</v>
-      </c>
-      <c r="M482" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="483" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A483" t="s">
+      <c r="H483" t="s">
+        <v>578</v>
+      </c>
+      <c r="M483" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="484" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A484" t="s">
         <v>474</v>
       </c>
-      <c r="B483" t="s">
+      <c r="B484" t="s">
         <v>539</v>
       </c>
-      <c r="D483" t="s">
-        <v>579</v>
-      </c>
-      <c r="E483" t="s">
-        <v>579</v>
-      </c>
-      <c r="F483" t="s">
-        <v>578</v>
-      </c>
-      <c r="G483" t="s">
-        <v>579</v>
-      </c>
-      <c r="H483" t="s">
-        <v>579</v>
-      </c>
-      <c r="J483" t="s">
-        <v>579</v>
-      </c>
-      <c r="K483" t="s">
-        <v>579</v>
-      </c>
-      <c r="M483" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="484" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A484" t="s">
+      <c r="D484" t="s">
+        <v>579</v>
+      </c>
+      <c r="E484" t="s">
+        <v>579</v>
+      </c>
+      <c r="F484" t="s">
+        <v>578</v>
+      </c>
+      <c r="G484" t="s">
+        <v>579</v>
+      </c>
+      <c r="H484" t="s">
+        <v>579</v>
+      </c>
+      <c r="J484" t="s">
+        <v>579</v>
+      </c>
+      <c r="K484" t="s">
+        <v>579</v>
+      </c>
+      <c r="M484" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="485" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A485" t="s">
         <v>624</v>
       </c>
-      <c r="B484" t="s">
+      <c r="B485" t="s">
         <v>638</v>
       </c>
-      <c r="D484" t="s">
-        <v>579</v>
-      </c>
-      <c r="E484" t="s">
-        <v>579</v>
-      </c>
-      <c r="F484" t="s">
-        <v>579</v>
-      </c>
-      <c r="G484" t="s">
-        <v>579</v>
-      </c>
-      <c r="H484" t="s">
-        <v>579</v>
-      </c>
-      <c r="I484" t="s">
-        <v>579</v>
-      </c>
-      <c r="J484" t="s">
-        <v>579</v>
-      </c>
-      <c r="K484" t="s">
-        <v>579</v>
-      </c>
-      <c r="M484" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="485" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A485" t="s">
+      <c r="D485" t="s">
+        <v>579</v>
+      </c>
+      <c r="E485" t="s">
+        <v>579</v>
+      </c>
+      <c r="F485" t="s">
+        <v>579</v>
+      </c>
+      <c r="G485" t="s">
+        <v>579</v>
+      </c>
+      <c r="H485" t="s">
+        <v>579</v>
+      </c>
+      <c r="I485" t="s">
+        <v>579</v>
+      </c>
+      <c r="J485" t="s">
+        <v>579</v>
+      </c>
+      <c r="K485" t="s">
+        <v>579</v>
+      </c>
+      <c r="M485" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="486" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A486" t="s">
         <v>587</v>
-      </c>
-      <c r="B485" t="s">
-        <v>539</v>
-      </c>
-      <c r="M485" t="s">
-        <v>579</v>
-      </c>
-      <c r="N485" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="486" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A486" t="s">
-        <v>588</v>
       </c>
       <c r="B486" t="s">
         <v>539</v>
@@ -9744,13 +9823,13 @@
       <c r="M486" t="s">
         <v>579</v>
       </c>
-      <c r="N486" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="487" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="O486" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="487" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A487" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B487" t="s">
         <v>539</v>
@@ -9758,73 +9837,76 @@
       <c r="M487" t="s">
         <v>579</v>
       </c>
-      <c r="N487" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="488" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="O487" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="488" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A488" t="s">
-        <v>475</v>
+        <v>589</v>
       </c>
       <c r="B488" t="s">
         <v>539</v>
       </c>
-      <c r="D488" t="s">
-        <v>579</v>
-      </c>
-      <c r="E488" t="s">
-        <v>579</v>
-      </c>
-      <c r="F488" t="s">
-        <v>578</v>
-      </c>
-      <c r="G488" t="s">
-        <v>579</v>
-      </c>
-      <c r="H488" t="s">
-        <v>579</v>
-      </c>
-      <c r="I488" t="s">
-        <v>579</v>
-      </c>
-      <c r="J488" t="s">
-        <v>579</v>
-      </c>
-      <c r="K488" t="s">
-        <v>579</v>
-      </c>
       <c r="M488" t="s">
         <v>579</v>
       </c>
-    </row>
-    <row r="489" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="O488" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="489" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A489" t="s">
+        <v>475</v>
+      </c>
+      <c r="B489" t="s">
+        <v>539</v>
+      </c>
+      <c r="D489" t="s">
+        <v>579</v>
+      </c>
+      <c r="E489" t="s">
+        <v>579</v>
+      </c>
+      <c r="F489" t="s">
+        <v>578</v>
+      </c>
+      <c r="G489" t="s">
+        <v>579</v>
+      </c>
+      <c r="H489" t="s">
+        <v>579</v>
+      </c>
+      <c r="I489" t="s">
+        <v>579</v>
+      </c>
+      <c r="J489" t="s">
+        <v>579</v>
+      </c>
+      <c r="K489" t="s">
+        <v>579</v>
+      </c>
+      <c r="M489" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="490" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A490" t="s">
         <v>590</v>
       </c>
-      <c r="B489" t="s">
+      <c r="B490" t="s">
         <v>541</v>
       </c>
-      <c r="M489" t="s">
-        <v>579</v>
-      </c>
-      <c r="N489" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="490" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A490" t="s">
+      <c r="M490" t="s">
+        <v>579</v>
+      </c>
+      <c r="O490" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="491" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A491" t="s">
         <v>625</v>
-      </c>
-      <c r="B490" t="s">
-        <v>539</v>
-      </c>
-      <c r="M490" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="491" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A491" t="s">
-        <v>626</v>
       </c>
       <c r="B491" t="s">
         <v>539</v>
@@ -9833,184 +9915,160 @@
         <v>578</v>
       </c>
     </row>
-    <row r="492" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="492" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A492" t="s">
+        <v>626</v>
+      </c>
+      <c r="B492" t="s">
+        <v>539</v>
+      </c>
+      <c r="M492" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="493" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A493" t="s">
         <v>476</v>
       </c>
-      <c r="B492" t="s">
+      <c r="B493" t="s">
         <v>541</v>
       </c>
-      <c r="D492" t="s">
-        <v>579</v>
-      </c>
-      <c r="E492" t="s">
-        <v>579</v>
-      </c>
-      <c r="F492" t="s">
-        <v>578</v>
-      </c>
-      <c r="G492" t="s">
-        <v>579</v>
-      </c>
-      <c r="H492" t="s">
-        <v>578</v>
-      </c>
-      <c r="I492" t="s">
-        <v>579</v>
-      </c>
-      <c r="J492" t="s">
-        <v>579</v>
-      </c>
-      <c r="K492" t="s">
-        <v>579</v>
-      </c>
-      <c r="M492" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="493" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A493" t="s">
+      <c r="D493" t="s">
+        <v>579</v>
+      </c>
+      <c r="E493" t="s">
+        <v>579</v>
+      </c>
+      <c r="F493" t="s">
+        <v>578</v>
+      </c>
+      <c r="G493" t="s">
+        <v>579</v>
+      </c>
+      <c r="H493" t="s">
+        <v>578</v>
+      </c>
+      <c r="I493" t="s">
+        <v>579</v>
+      </c>
+      <c r="J493" t="s">
+        <v>579</v>
+      </c>
+      <c r="K493" t="s">
+        <v>579</v>
+      </c>
+      <c r="M493" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="494" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A494" t="s">
         <v>477</v>
       </c>
-      <c r="B493" t="s">
+      <c r="B494" t="s">
         <v>544</v>
       </c>
-      <c r="D493" t="s">
-        <v>578</v>
-      </c>
-      <c r="E493" t="s">
-        <v>579</v>
-      </c>
-      <c r="F493" t="s">
-        <v>578</v>
-      </c>
-      <c r="G493" t="s">
-        <v>579</v>
-      </c>
-      <c r="H493" t="s">
-        <v>579</v>
-      </c>
-      <c r="I493" t="s">
-        <v>579</v>
-      </c>
-      <c r="J493" t="s">
-        <v>579</v>
-      </c>
-      <c r="K493" t="s">
-        <v>578</v>
-      </c>
-      <c r="M493" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="494" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A494" t="s">
+      <c r="D494" t="s">
+        <v>578</v>
+      </c>
+      <c r="E494" t="s">
+        <v>579</v>
+      </c>
+      <c r="F494" t="s">
+        <v>578</v>
+      </c>
+      <c r="G494" t="s">
+        <v>579</v>
+      </c>
+      <c r="H494" t="s">
+        <v>579</v>
+      </c>
+      <c r="I494" t="s">
+        <v>579</v>
+      </c>
+      <c r="J494" t="s">
+        <v>579</v>
+      </c>
+      <c r="K494" t="s">
+        <v>578</v>
+      </c>
+      <c r="M494" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="495" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A495" t="s">
         <v>478</v>
       </c>
-      <c r="B494" t="s">
+      <c r="B495" t="s">
         <v>537</v>
       </c>
-      <c r="D494" t="s">
-        <v>579</v>
-      </c>
-      <c r="E494" t="s">
-        <v>579</v>
-      </c>
-      <c r="F494" t="s">
-        <v>579</v>
-      </c>
-      <c r="G494" t="s">
-        <v>579</v>
-      </c>
-      <c r="H494" t="s">
-        <v>579</v>
-      </c>
-      <c r="I494" t="s">
-        <v>579</v>
-      </c>
-      <c r="J494" t="s">
-        <v>579</v>
-      </c>
-      <c r="K494" t="s">
-        <v>578</v>
-      </c>
-      <c r="M494" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="495" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A495" t="s">
+      <c r="D495" t="s">
+        <v>579</v>
+      </c>
+      <c r="E495" t="s">
+        <v>579</v>
+      </c>
+      <c r="F495" t="s">
+        <v>579</v>
+      </c>
+      <c r="G495" t="s">
+        <v>579</v>
+      </c>
+      <c r="H495" t="s">
+        <v>579</v>
+      </c>
+      <c r="I495" t="s">
+        <v>579</v>
+      </c>
+      <c r="J495" t="s">
+        <v>579</v>
+      </c>
+      <c r="K495" t="s">
+        <v>578</v>
+      </c>
+      <c r="M495" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="496" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A496" t="s">
         <v>479</v>
       </c>
-      <c r="B495" t="s">
-        <v>538</v>
-      </c>
-      <c r="D495" t="s">
-        <v>579</v>
-      </c>
-      <c r="E495" t="s">
-        <v>579</v>
-      </c>
-      <c r="F495" t="s">
-        <v>579</v>
-      </c>
-      <c r="G495" t="s">
-        <v>579</v>
-      </c>
-      <c r="H495" t="s">
-        <v>579</v>
-      </c>
-      <c r="I495" t="s">
-        <v>579</v>
-      </c>
-      <c r="J495" t="s">
-        <v>578</v>
-      </c>
-      <c r="K495" t="s">
-        <v>579</v>
-      </c>
-      <c r="M495" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="496" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A496" t="s">
+      <c r="B496" t="s">
+        <v>538</v>
+      </c>
+      <c r="D496" t="s">
+        <v>579</v>
+      </c>
+      <c r="E496" t="s">
+        <v>579</v>
+      </c>
+      <c r="F496" t="s">
+        <v>579</v>
+      </c>
+      <c r="G496" t="s">
+        <v>579</v>
+      </c>
+      <c r="H496" t="s">
+        <v>579</v>
+      </c>
+      <c r="I496" t="s">
+        <v>579</v>
+      </c>
+      <c r="J496" t="s">
+        <v>578</v>
+      </c>
+      <c r="K496" t="s">
+        <v>579</v>
+      </c>
+      <c r="M496" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="497" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A497" t="s">
         <v>480</v>
-      </c>
-      <c r="B496" t="s">
-        <v>539</v>
-      </c>
-      <c r="D496" t="s">
-        <v>578</v>
-      </c>
-      <c r="E496" t="s">
-        <v>579</v>
-      </c>
-      <c r="F496" t="s">
-        <v>578</v>
-      </c>
-      <c r="G496" t="s">
-        <v>579</v>
-      </c>
-      <c r="H496" t="s">
-        <v>579</v>
-      </c>
-      <c r="I496" t="s">
-        <v>579</v>
-      </c>
-      <c r="J496" t="s">
-        <v>579</v>
-      </c>
-      <c r="K496" t="s">
-        <v>578</v>
-      </c>
-      <c r="M496" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="497" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A497" t="s">
-        <v>481</v>
       </c>
       <c r="B497" t="s">
         <v>539</v>
@@ -10022,7 +10080,7 @@
         <v>579</v>
       </c>
       <c r="F497" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="G497" t="s">
         <v>579</v>
@@ -10037,99 +10095,99 @@
         <v>579</v>
       </c>
       <c r="K497" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="M497" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="498" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="498" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A498" t="s">
+        <v>481</v>
+      </c>
+      <c r="B498" t="s">
+        <v>539</v>
+      </c>
+      <c r="D498" t="s">
+        <v>578</v>
+      </c>
+      <c r="E498" t="s">
+        <v>579</v>
+      </c>
+      <c r="F498" t="s">
+        <v>579</v>
+      </c>
+      <c r="G498" t="s">
+        <v>579</v>
+      </c>
+      <c r="H498" t="s">
+        <v>579</v>
+      </c>
+      <c r="I498" t="s">
+        <v>579</v>
+      </c>
+      <c r="J498" t="s">
+        <v>579</v>
+      </c>
+      <c r="K498" t="s">
+        <v>579</v>
+      </c>
+      <c r="M498" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="499" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A499" t="s">
         <v>482</v>
       </c>
-      <c r="B498" t="s">
+      <c r="B499" t="s">
         <v>543</v>
       </c>
-      <c r="J498" t="s">
-        <v>578</v>
-      </c>
-      <c r="M498" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="499" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A499" t="s">
+      <c r="J499" t="s">
+        <v>578</v>
+      </c>
+      <c r="M499" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="500" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A500" t="s">
         <v>483</v>
       </c>
-      <c r="B499" t="s">
+      <c r="B500" t="s">
         <v>541</v>
       </c>
-      <c r="D499" t="s">
-        <v>579</v>
-      </c>
-      <c r="E499" t="s">
-        <v>579</v>
-      </c>
-      <c r="F499" t="s">
-        <v>578</v>
-      </c>
-      <c r="G499" t="s">
-        <v>579</v>
-      </c>
-      <c r="H499" t="s">
-        <v>578</v>
-      </c>
-      <c r="I499" t="s">
-        <v>579</v>
-      </c>
-      <c r="J499" t="s">
-        <v>578</v>
-      </c>
-      <c r="K499" t="s">
-        <v>579</v>
-      </c>
-      <c r="M499" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="500" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A500" t="s">
+      <c r="D500" t="s">
+        <v>579</v>
+      </c>
+      <c r="E500" t="s">
+        <v>579</v>
+      </c>
+      <c r="F500" t="s">
+        <v>578</v>
+      </c>
+      <c r="G500" t="s">
+        <v>579</v>
+      </c>
+      <c r="H500" t="s">
+        <v>578</v>
+      </c>
+      <c r="I500" t="s">
+        <v>579</v>
+      </c>
+      <c r="J500" t="s">
+        <v>578</v>
+      </c>
+      <c r="K500" t="s">
+        <v>579</v>
+      </c>
+      <c r="M500" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="501" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A501" t="s">
         <v>484</v>
-      </c>
-      <c r="B500" t="s">
-        <v>543</v>
-      </c>
-      <c r="D500" t="s">
-        <v>579</v>
-      </c>
-      <c r="E500" t="s">
-        <v>579</v>
-      </c>
-      <c r="F500" t="s">
-        <v>579</v>
-      </c>
-      <c r="G500" t="s">
-        <v>579</v>
-      </c>
-      <c r="H500" t="s">
-        <v>579</v>
-      </c>
-      <c r="I500" t="s">
-        <v>579</v>
-      </c>
-      <c r="J500" t="s">
-        <v>578</v>
-      </c>
-      <c r="K500" t="s">
-        <v>579</v>
-      </c>
-      <c r="M500" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="501" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A501" t="s">
-        <v>485</v>
       </c>
       <c r="B501" t="s">
         <v>543</v>
@@ -10150,10 +10208,10 @@
         <v>579</v>
       </c>
       <c r="I501" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="J501" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="K501" t="s">
         <v>579</v>
@@ -10162,149 +10220,149 @@
         <v>579</v>
       </c>
     </row>
-    <row r="502" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="502" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A502" t="s">
+        <v>485</v>
+      </c>
+      <c r="B502" t="s">
+        <v>543</v>
+      </c>
+      <c r="D502" t="s">
+        <v>579</v>
+      </c>
+      <c r="E502" t="s">
+        <v>579</v>
+      </c>
+      <c r="F502" t="s">
+        <v>579</v>
+      </c>
+      <c r="G502" t="s">
+        <v>579</v>
+      </c>
+      <c r="H502" t="s">
+        <v>579</v>
+      </c>
+      <c r="I502" t="s">
+        <v>578</v>
+      </c>
+      <c r="J502" t="s">
+        <v>579</v>
+      </c>
+      <c r="K502" t="s">
+        <v>579</v>
+      </c>
+      <c r="M502" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="503" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A503" t="s">
         <v>486</v>
       </c>
-      <c r="B502" t="s">
+      <c r="B503" t="s">
         <v>541</v>
       </c>
-      <c r="D502" t="s">
-        <v>579</v>
-      </c>
-      <c r="E502" t="s">
-        <v>579</v>
-      </c>
-      <c r="F502" t="s">
-        <v>578</v>
-      </c>
-      <c r="G502" t="s">
-        <v>579</v>
-      </c>
-      <c r="H502" t="s">
-        <v>578</v>
-      </c>
-      <c r="I502" t="s">
-        <v>579</v>
-      </c>
-      <c r="J502" t="s">
-        <v>579</v>
-      </c>
-      <c r="K502" t="s">
-        <v>579</v>
-      </c>
-      <c r="M502" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="503" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A503" t="s">
+      <c r="D503" t="s">
+        <v>579</v>
+      </c>
+      <c r="E503" t="s">
+        <v>579</v>
+      </c>
+      <c r="F503" t="s">
+        <v>578</v>
+      </c>
+      <c r="G503" t="s">
+        <v>579</v>
+      </c>
+      <c r="H503" t="s">
+        <v>578</v>
+      </c>
+      <c r="I503" t="s">
+        <v>579</v>
+      </c>
+      <c r="J503" t="s">
+        <v>579</v>
+      </c>
+      <c r="K503" t="s">
+        <v>579</v>
+      </c>
+      <c r="M503" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="504" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A504" t="s">
         <v>487</v>
       </c>
-      <c r="B503" t="s">
+      <c r="B504" t="s">
         <v>543</v>
       </c>
-      <c r="D503" t="s">
-        <v>579</v>
-      </c>
-      <c r="E503" t="s">
-        <v>579</v>
-      </c>
-      <c r="F503" t="s">
-        <v>579</v>
-      </c>
-      <c r="G503" t="s">
-        <v>579</v>
-      </c>
-      <c r="H503" t="s">
-        <v>579</v>
-      </c>
-      <c r="I503" t="s">
-        <v>578</v>
-      </c>
-      <c r="J503" t="s">
-        <v>579</v>
-      </c>
-      <c r="K503" t="s">
-        <v>579</v>
-      </c>
-      <c r="M503" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="504" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A504" t="s">
+      <c r="D504" t="s">
+        <v>579</v>
+      </c>
+      <c r="E504" t="s">
+        <v>579</v>
+      </c>
+      <c r="F504" t="s">
+        <v>579</v>
+      </c>
+      <c r="G504" t="s">
+        <v>579</v>
+      </c>
+      <c r="H504" t="s">
+        <v>579</v>
+      </c>
+      <c r="I504" t="s">
+        <v>578</v>
+      </c>
+      <c r="J504" t="s">
+        <v>579</v>
+      </c>
+      <c r="K504" t="s">
+        <v>579</v>
+      </c>
+      <c r="M504" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="505" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A505" t="s">
         <v>488</v>
       </c>
-      <c r="B504" t="s">
+      <c r="B505" t="s">
         <v>541</v>
       </c>
-      <c r="D504" t="s">
-        <v>579</v>
-      </c>
-      <c r="E504" t="s">
-        <v>579</v>
-      </c>
-      <c r="F504" t="s">
-        <v>578</v>
-      </c>
-      <c r="G504" t="s">
-        <v>579</v>
-      </c>
-      <c r="H504" t="s">
-        <v>578</v>
-      </c>
-      <c r="I504" t="s">
-        <v>579</v>
-      </c>
-      <c r="J504" t="s">
-        <v>578</v>
-      </c>
-      <c r="K504" t="s">
-        <v>579</v>
-      </c>
-      <c r="M504" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="505" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A505" t="s">
+      <c r="D505" t="s">
+        <v>579</v>
+      </c>
+      <c r="E505" t="s">
+        <v>579</v>
+      </c>
+      <c r="F505" t="s">
+        <v>578</v>
+      </c>
+      <c r="G505" t="s">
+        <v>579</v>
+      </c>
+      <c r="H505" t="s">
+        <v>578</v>
+      </c>
+      <c r="I505" t="s">
+        <v>579</v>
+      </c>
+      <c r="J505" t="s">
+        <v>578</v>
+      </c>
+      <c r="K505" t="s">
+        <v>579</v>
+      </c>
+      <c r="M505" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="506" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A506" t="s">
         <v>489</v>
-      </c>
-      <c r="B505" t="s">
-        <v>543</v>
-      </c>
-      <c r="D505" t="s">
-        <v>579</v>
-      </c>
-      <c r="E505" t="s">
-        <v>579</v>
-      </c>
-      <c r="F505" t="s">
-        <v>579</v>
-      </c>
-      <c r="G505" t="s">
-        <v>579</v>
-      </c>
-      <c r="H505" t="s">
-        <v>579</v>
-      </c>
-      <c r="I505" t="s">
-        <v>578</v>
-      </c>
-      <c r="J505" t="s">
-        <v>579</v>
-      </c>
-      <c r="K505" t="s">
-        <v>579</v>
-      </c>
-      <c r="M505" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="506" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A506" t="s">
-        <v>490</v>
       </c>
       <c r="B506" t="s">
         <v>543</v>
@@ -10328,7 +10386,7 @@
         <v>578</v>
       </c>
       <c r="J506" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="K506" t="s">
         <v>579</v>
@@ -10337,9 +10395,9 @@
         <v>579</v>
       </c>
     </row>
-    <row r="507" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="507" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A507" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B507" t="s">
         <v>543</v>
@@ -10363,7 +10421,7 @@
         <v>578</v>
       </c>
       <c r="J507" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="K507" t="s">
         <v>579</v>
@@ -10372,9 +10430,9 @@
         <v>579</v>
       </c>
     </row>
-    <row r="508" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="508" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A508" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B508" t="s">
         <v>543</v>
@@ -10395,10 +10453,10 @@
         <v>579</v>
       </c>
       <c r="I508" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="J508" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="K508" t="s">
         <v>579</v>
@@ -10407,93 +10465,93 @@
         <v>579</v>
       </c>
     </row>
-    <row r="509" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="509" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A509" t="s">
+        <v>492</v>
+      </c>
+      <c r="B509" t="s">
+        <v>543</v>
+      </c>
+      <c r="D509" t="s">
+        <v>579</v>
+      </c>
+      <c r="E509" t="s">
+        <v>579</v>
+      </c>
+      <c r="F509" t="s">
+        <v>579</v>
+      </c>
+      <c r="G509" t="s">
+        <v>579</v>
+      </c>
+      <c r="H509" t="s">
+        <v>579</v>
+      </c>
+      <c r="I509" t="s">
+        <v>579</v>
+      </c>
+      <c r="J509" t="s">
+        <v>578</v>
+      </c>
+      <c r="K509" t="s">
+        <v>579</v>
+      </c>
+      <c r="M509" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="510" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A510" t="s">
         <v>591</v>
       </c>
-      <c r="B509" t="s">
+      <c r="B510" t="s">
         <v>539</v>
       </c>
-      <c r="M509" t="s">
-        <v>579</v>
-      </c>
-      <c r="N509" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="510" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A510" t="s">
+      <c r="M510" t="s">
+        <v>579</v>
+      </c>
+      <c r="O510" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="511" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A511" t="s">
         <v>493</v>
       </c>
-      <c r="B510" t="s">
+      <c r="B511" t="s">
         <v>541</v>
       </c>
-      <c r="D510" t="s">
-        <v>579</v>
-      </c>
-      <c r="E510" t="s">
-        <v>579</v>
-      </c>
-      <c r="F510" t="s">
-        <v>578</v>
-      </c>
-      <c r="G510" t="s">
-        <v>579</v>
-      </c>
-      <c r="H510" t="s">
-        <v>578</v>
-      </c>
-      <c r="I510" t="s">
-        <v>579</v>
-      </c>
-      <c r="J510" t="s">
-        <v>579</v>
-      </c>
-      <c r="K510" t="s">
-        <v>579</v>
-      </c>
-      <c r="M510" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="511" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A511" t="s">
+      <c r="D511" t="s">
+        <v>579</v>
+      </c>
+      <c r="E511" t="s">
+        <v>579</v>
+      </c>
+      <c r="F511" t="s">
+        <v>578</v>
+      </c>
+      <c r="G511" t="s">
+        <v>579</v>
+      </c>
+      <c r="H511" t="s">
+        <v>578</v>
+      </c>
+      <c r="I511" t="s">
+        <v>579</v>
+      </c>
+      <c r="J511" t="s">
+        <v>579</v>
+      </c>
+      <c r="K511" t="s">
+        <v>579</v>
+      </c>
+      <c r="M511" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="512" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A512" t="s">
         <v>494</v>
-      </c>
-      <c r="B511" t="s">
-        <v>543</v>
-      </c>
-      <c r="D511" t="s">
-        <v>579</v>
-      </c>
-      <c r="E511" t="s">
-        <v>579</v>
-      </c>
-      <c r="F511" t="s">
-        <v>579</v>
-      </c>
-      <c r="G511" t="s">
-        <v>579</v>
-      </c>
-      <c r="H511" t="s">
-        <v>579</v>
-      </c>
-      <c r="I511" t="s">
-        <v>579</v>
-      </c>
-      <c r="J511" t="s">
-        <v>578</v>
-      </c>
-      <c r="K511" t="s">
-        <v>579</v>
-      </c>
-      <c r="M511" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="512" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A512" t="s">
-        <v>495</v>
       </c>
       <c r="B512" t="s">
         <v>543</v>
@@ -10517,7 +10575,7 @@
         <v>579</v>
       </c>
       <c r="J512" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="K512" t="s">
         <v>579</v>
@@ -10525,13 +10583,10 @@
       <c r="M512" t="s">
         <v>579</v>
       </c>
-      <c r="N512" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="513" spans="1:14" x14ac:dyDescent="0.4">
+    </row>
+    <row r="513" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A513" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B513" t="s">
         <v>543</v>
@@ -10563,83 +10618,86 @@
       <c r="M513" t="s">
         <v>579</v>
       </c>
-      <c r="N513" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="514" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="O513" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="514" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A514" t="s">
+        <v>496</v>
+      </c>
+      <c r="B514" t="s">
+        <v>543</v>
+      </c>
+      <c r="D514" t="s">
+        <v>579</v>
+      </c>
+      <c r="E514" t="s">
+        <v>579</v>
+      </c>
+      <c r="F514" t="s">
+        <v>579</v>
+      </c>
+      <c r="G514" t="s">
+        <v>579</v>
+      </c>
+      <c r="H514" t="s">
+        <v>579</v>
+      </c>
+      <c r="I514" t="s">
+        <v>579</v>
+      </c>
+      <c r="J514" t="s">
+        <v>579</v>
+      </c>
+      <c r="K514" t="s">
+        <v>579</v>
+      </c>
+      <c r="M514" t="s">
+        <v>579</v>
+      </c>
+      <c r="O514" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="515" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A515" t="s">
         <v>497</v>
       </c>
-      <c r="B514" t="s">
+      <c r="B515" t="s">
         <v>541</v>
       </c>
-      <c r="D514" t="s">
-        <v>579</v>
-      </c>
-      <c r="E514" t="s">
-        <v>579</v>
-      </c>
-      <c r="F514" t="s">
-        <v>578</v>
-      </c>
-      <c r="G514" t="s">
-        <v>579</v>
-      </c>
-      <c r="H514" t="s">
-        <v>578</v>
-      </c>
-      <c r="I514" t="s">
-        <v>579</v>
-      </c>
-      <c r="J514" t="s">
-        <v>579</v>
-      </c>
-      <c r="K514" t="s">
-        <v>579</v>
-      </c>
-      <c r="M514" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="515" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A515" t="s">
+      <c r="D515" t="s">
+        <v>579</v>
+      </c>
+      <c r="E515" t="s">
+        <v>579</v>
+      </c>
+      <c r="F515" t="s">
+        <v>578</v>
+      </c>
+      <c r="G515" t="s">
+        <v>579</v>
+      </c>
+      <c r="H515" t="s">
+        <v>578</v>
+      </c>
+      <c r="I515" t="s">
+        <v>579</v>
+      </c>
+      <c r="J515" t="s">
+        <v>579</v>
+      </c>
+      <c r="K515" t="s">
+        <v>579</v>
+      </c>
+      <c r="M515" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="516" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A516" t="s">
         <v>498</v>
-      </c>
-      <c r="B515" t="s">
-        <v>543</v>
-      </c>
-      <c r="D515" t="s">
-        <v>579</v>
-      </c>
-      <c r="E515" t="s">
-        <v>579</v>
-      </c>
-      <c r="F515" t="s">
-        <v>579</v>
-      </c>
-      <c r="G515" t="s">
-        <v>579</v>
-      </c>
-      <c r="H515" t="s">
-        <v>579</v>
-      </c>
-      <c r="I515" t="s">
-        <v>579</v>
-      </c>
-      <c r="J515" t="s">
-        <v>578</v>
-      </c>
-      <c r="K515" t="s">
-        <v>579</v>
-      </c>
-      <c r="M515" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="516" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A516" t="s">
-        <v>499</v>
       </c>
       <c r="B516" t="s">
         <v>543</v>
@@ -10663,7 +10721,7 @@
         <v>579</v>
       </c>
       <c r="J516" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="K516" t="s">
         <v>579</v>
@@ -10671,13 +10729,10 @@
       <c r="M516" t="s">
         <v>579</v>
       </c>
-      <c r="N516" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="517" spans="1:14" x14ac:dyDescent="0.4">
+    </row>
+    <row r="517" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A517" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B517" t="s">
         <v>543</v>
@@ -10698,21 +10753,24 @@
         <v>579</v>
       </c>
       <c r="I517" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="J517" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="K517" t="s">
         <v>579</v>
       </c>
       <c r="M517" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="518" spans="1:14" x14ac:dyDescent="0.4">
+        <v>579</v>
+      </c>
+      <c r="O517" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="518" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A518" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B518" t="s">
         <v>543</v>
@@ -10736,88 +10794,88 @@
         <v>578</v>
       </c>
       <c r="J518" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="K518" t="s">
         <v>579</v>
       </c>
       <c r="M518" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="519" spans="1:14" x14ac:dyDescent="0.4">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="519" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A519" t="s">
+        <v>501</v>
+      </c>
+      <c r="B519" t="s">
+        <v>543</v>
+      </c>
+      <c r="D519" t="s">
+        <v>579</v>
+      </c>
+      <c r="E519" t="s">
+        <v>579</v>
+      </c>
+      <c r="F519" t="s">
+        <v>579</v>
+      </c>
+      <c r="G519" t="s">
+        <v>579</v>
+      </c>
+      <c r="H519" t="s">
+        <v>579</v>
+      </c>
+      <c r="I519" t="s">
+        <v>578</v>
+      </c>
+      <c r="J519" t="s">
+        <v>579</v>
+      </c>
+      <c r="K519" t="s">
+        <v>579</v>
+      </c>
+      <c r="M519" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="520" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A520" t="s">
         <v>502</v>
       </c>
-      <c r="B519" t="s">
+      <c r="B520" t="s">
         <v>541</v>
       </c>
-      <c r="D519" t="s">
-        <v>579</v>
-      </c>
-      <c r="E519" t="s">
-        <v>579</v>
-      </c>
-      <c r="F519" t="s">
-        <v>578</v>
-      </c>
-      <c r="G519" t="s">
-        <v>579</v>
-      </c>
-      <c r="H519" t="s">
-        <v>578</v>
-      </c>
-      <c r="I519" t="s">
-        <v>579</v>
-      </c>
-      <c r="J519" t="s">
-        <v>578</v>
-      </c>
-      <c r="K519" t="s">
-        <v>579</v>
-      </c>
-      <c r="M519" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="520" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A520" t="s">
+      <c r="D520" t="s">
+        <v>579</v>
+      </c>
+      <c r="E520" t="s">
+        <v>579</v>
+      </c>
+      <c r="F520" t="s">
+        <v>578</v>
+      </c>
+      <c r="G520" t="s">
+        <v>579</v>
+      </c>
+      <c r="H520" t="s">
+        <v>578</v>
+      </c>
+      <c r="I520" t="s">
+        <v>579</v>
+      </c>
+      <c r="J520" t="s">
+        <v>578</v>
+      </c>
+      <c r="K520" t="s">
+        <v>579</v>
+      </c>
+      <c r="M520" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="521" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A521" t="s">
         <v>503</v>
-      </c>
-      <c r="B520" t="s">
-        <v>543</v>
-      </c>
-      <c r="D520" t="s">
-        <v>579</v>
-      </c>
-      <c r="E520" t="s">
-        <v>579</v>
-      </c>
-      <c r="F520" t="s">
-        <v>578</v>
-      </c>
-      <c r="G520" t="s">
-        <v>579</v>
-      </c>
-      <c r="H520" t="s">
-        <v>579</v>
-      </c>
-      <c r="I520" t="s">
-        <v>579</v>
-      </c>
-      <c r="J520" t="s">
-        <v>578</v>
-      </c>
-      <c r="K520" t="s">
-        <v>578</v>
-      </c>
-      <c r="M520" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="521" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A521" t="s">
-        <v>504</v>
       </c>
       <c r="B521" t="s">
         <v>543</v>
@@ -10829,7 +10887,7 @@
         <v>579</v>
       </c>
       <c r="F521" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="G521" t="s">
         <v>579</v>
@@ -10844,50 +10902,50 @@
         <v>578</v>
       </c>
       <c r="K521" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="M521" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="522" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="522" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A522" t="s">
+        <v>504</v>
+      </c>
+      <c r="B522" t="s">
+        <v>543</v>
+      </c>
+      <c r="D522" t="s">
+        <v>579</v>
+      </c>
+      <c r="E522" t="s">
+        <v>579</v>
+      </c>
+      <c r="F522" t="s">
+        <v>579</v>
+      </c>
+      <c r="G522" t="s">
+        <v>579</v>
+      </c>
+      <c r="H522" t="s">
+        <v>579</v>
+      </c>
+      <c r="I522" t="s">
+        <v>579</v>
+      </c>
+      <c r="J522" t="s">
+        <v>578</v>
+      </c>
+      <c r="K522" t="s">
+        <v>579</v>
+      </c>
+      <c r="M522" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="523" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A523" t="s">
         <v>505</v>
-      </c>
-      <c r="B522" t="s">
-        <v>541</v>
-      </c>
-      <c r="D522" t="s">
-        <v>579</v>
-      </c>
-      <c r="E522" t="s">
-        <v>579</v>
-      </c>
-      <c r="F522" t="s">
-        <v>578</v>
-      </c>
-      <c r="G522" t="s">
-        <v>579</v>
-      </c>
-      <c r="H522" t="s">
-        <v>578</v>
-      </c>
-      <c r="I522" t="s">
-        <v>579</v>
-      </c>
-      <c r="J522" t="s">
-        <v>578</v>
-      </c>
-      <c r="K522" t="s">
-        <v>578</v>
-      </c>
-      <c r="M522" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="523" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A523" t="s">
-        <v>506</v>
       </c>
       <c r="B523" t="s">
         <v>541</v>
@@ -10899,13 +10957,13 @@
         <v>579</v>
       </c>
       <c r="F523" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="G523" t="s">
         <v>579</v>
       </c>
       <c r="H523" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="I523" t="s">
         <v>579</v>
@@ -10914,15 +10972,15 @@
         <v>578</v>
       </c>
       <c r="K523" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="M523" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="524" spans="1:14" x14ac:dyDescent="0.4">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="524" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A524" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B524" t="s">
         <v>541</v>
@@ -10954,45 +11012,48 @@
       <c r="M524" t="s">
         <v>579</v>
       </c>
-    </row>
-    <row r="525" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="N524" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="525" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A525" t="s">
+        <v>507</v>
+      </c>
+      <c r="B525" t="s">
+        <v>541</v>
+      </c>
+      <c r="D525" t="s">
+        <v>579</v>
+      </c>
+      <c r="E525" t="s">
+        <v>579</v>
+      </c>
+      <c r="F525" t="s">
+        <v>579</v>
+      </c>
+      <c r="G525" t="s">
+        <v>579</v>
+      </c>
+      <c r="H525" t="s">
+        <v>579</v>
+      </c>
+      <c r="I525" t="s">
+        <v>579</v>
+      </c>
+      <c r="J525" t="s">
+        <v>578</v>
+      </c>
+      <c r="K525" t="s">
+        <v>579</v>
+      </c>
+      <c r="M525" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="526" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A526" t="s">
         <v>508</v>
-      </c>
-      <c r="B525" t="s">
-        <v>543</v>
-      </c>
-      <c r="D525" t="s">
-        <v>579</v>
-      </c>
-      <c r="E525" t="s">
-        <v>579</v>
-      </c>
-      <c r="F525" t="s">
-        <v>579</v>
-      </c>
-      <c r="G525" t="s">
-        <v>579</v>
-      </c>
-      <c r="H525" t="s">
-        <v>579</v>
-      </c>
-      <c r="I525" t="s">
-        <v>579</v>
-      </c>
-      <c r="J525" t="s">
-        <v>578</v>
-      </c>
-      <c r="K525" t="s">
-        <v>579</v>
-      </c>
-      <c r="M525" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="526" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A526" t="s">
-        <v>509</v>
       </c>
       <c r="B526" t="s">
         <v>543</v>
@@ -11013,10 +11074,10 @@
         <v>579</v>
       </c>
       <c r="I526" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="J526" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="K526" t="s">
         <v>579</v>
@@ -11025,9 +11086,9 @@
         <v>579</v>
       </c>
     </row>
-    <row r="527" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="527" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A527" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B527" t="s">
         <v>543</v>
@@ -11048,10 +11109,10 @@
         <v>579</v>
       </c>
       <c r="I527" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="J527" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="K527" t="s">
         <v>579</v>
@@ -11060,9 +11121,9 @@
         <v>579</v>
       </c>
     </row>
-    <row r="528" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="528" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A528" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B528" t="s">
         <v>543</v>
@@ -11095,9 +11156,9 @@
         <v>579</v>
       </c>
     </row>
-    <row r="529" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="529" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A529" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B529" t="s">
         <v>543</v>
@@ -11121,7 +11182,7 @@
         <v>579</v>
       </c>
       <c r="J529" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="K529" t="s">
         <v>579</v>
@@ -11129,13 +11190,10 @@
       <c r="M529" t="s">
         <v>579</v>
       </c>
-      <c r="N529" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="530" spans="1:14" x14ac:dyDescent="0.4">
+    </row>
+    <row r="530" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A530" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B530" t="s">
         <v>543</v>
@@ -11156,7 +11214,7 @@
         <v>579</v>
       </c>
       <c r="I530" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="J530" t="s">
         <v>579</v>
@@ -11167,62 +11225,62 @@
       <c r="M530" t="s">
         <v>579</v>
       </c>
-    </row>
-    <row r="531" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="O530" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="531" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A531" t="s">
-        <v>592</v>
+        <v>513</v>
       </c>
       <c r="B531" t="s">
         <v>543</v>
       </c>
+      <c r="D531" t="s">
+        <v>579</v>
+      </c>
+      <c r="E531" t="s">
+        <v>579</v>
+      </c>
+      <c r="F531" t="s">
+        <v>579</v>
+      </c>
+      <c r="G531" t="s">
+        <v>579</v>
+      </c>
+      <c r="H531" t="s">
+        <v>579</v>
+      </c>
+      <c r="I531" t="s">
+        <v>578</v>
+      </c>
+      <c r="J531" t="s">
+        <v>579</v>
+      </c>
+      <c r="K531" t="s">
+        <v>579</v>
+      </c>
       <c r="M531" t="s">
         <v>579</v>
       </c>
-      <c r="N531" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="532" spans="1:14" x14ac:dyDescent="0.4">
+    </row>
+    <row r="532" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A532" t="s">
-        <v>514</v>
+        <v>592</v>
       </c>
       <c r="B532" t="s">
         <v>543</v>
       </c>
-      <c r="D532" t="s">
-        <v>579</v>
-      </c>
-      <c r="E532" t="s">
-        <v>579</v>
-      </c>
-      <c r="F532" t="s">
-        <v>579</v>
-      </c>
-      <c r="G532" t="s">
-        <v>579</v>
-      </c>
-      <c r="H532" t="s">
-        <v>579</v>
-      </c>
-      <c r="I532" t="s">
-        <v>579</v>
-      </c>
-      <c r="J532" t="s">
-        <v>579</v>
-      </c>
-      <c r="K532" t="s">
-        <v>579</v>
-      </c>
       <c r="M532" t="s">
         <v>579</v>
       </c>
-      <c r="N532" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="533" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="O532" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="533" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A533" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B533" t="s">
         <v>543</v>
@@ -11246,165 +11304,168 @@
         <v>579</v>
       </c>
       <c r="J533" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="K533" t="s">
         <v>579</v>
       </c>
       <c r="M533" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="534" spans="1:14" x14ac:dyDescent="0.4">
+        <v>579</v>
+      </c>
+      <c r="O533" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="534" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A534" t="s">
-        <v>593</v>
+        <v>515</v>
       </c>
       <c r="B534" t="s">
         <v>543</v>
       </c>
-      <c r="L534" t="s">
-        <v>578</v>
+      <c r="D534" t="s">
+        <v>579</v>
+      </c>
+      <c r="E534" t="s">
+        <v>579</v>
+      </c>
+      <c r="F534" t="s">
+        <v>579</v>
+      </c>
+      <c r="G534" t="s">
+        <v>579</v>
+      </c>
+      <c r="H534" t="s">
+        <v>579</v>
+      </c>
+      <c r="I534" t="s">
+        <v>579</v>
+      </c>
+      <c r="J534" t="s">
+        <v>578</v>
+      </c>
+      <c r="K534" t="s">
+        <v>579</v>
       </c>
       <c r="M534" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="535" spans="1:14" x14ac:dyDescent="0.4">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="535" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A535" t="s">
+        <v>593</v>
+      </c>
+      <c r="B535" t="s">
+        <v>543</v>
+      </c>
+      <c r="L535" t="s">
+        <v>578</v>
+      </c>
+      <c r="M535" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="536" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A536" t="s">
         <v>516</v>
-      </c>
-      <c r="B535" t="s">
-        <v>541</v>
-      </c>
-      <c r="D535" t="s">
-        <v>579</v>
-      </c>
-      <c r="E535" t="s">
-        <v>579</v>
-      </c>
-      <c r="F535" t="s">
-        <v>578</v>
-      </c>
-      <c r="G535" t="s">
-        <v>579</v>
-      </c>
-      <c r="H535" t="s">
-        <v>578</v>
-      </c>
-      <c r="I535" t="s">
-        <v>579</v>
-      </c>
-      <c r="J535" t="s">
-        <v>579</v>
-      </c>
-      <c r="K535" t="s">
-        <v>578</v>
-      </c>
-      <c r="M535" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="536" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A536" t="s">
-        <v>517</v>
       </c>
       <c r="B536" t="s">
         <v>541</v>
       </c>
+      <c r="D536" t="s">
+        <v>579</v>
+      </c>
+      <c r="E536" t="s">
+        <v>579</v>
+      </c>
+      <c r="F536" t="s">
+        <v>578</v>
+      </c>
+      <c r="G536" t="s">
+        <v>579</v>
+      </c>
       <c r="H536" t="s">
         <v>578</v>
       </c>
+      <c r="I536" t="s">
+        <v>579</v>
+      </c>
+      <c r="J536" t="s">
+        <v>579</v>
+      </c>
+      <c r="K536" t="s">
+        <v>578</v>
+      </c>
       <c r="M536" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="537" spans="1:14" x14ac:dyDescent="0.4">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="537" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A537" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B537" t="s">
         <v>541</v>
       </c>
-      <c r="D537" t="s">
-        <v>579</v>
-      </c>
-      <c r="E537" t="s">
-        <v>579</v>
-      </c>
-      <c r="F537" t="s">
-        <v>578</v>
-      </c>
-      <c r="G537" t="s">
-        <v>579</v>
-      </c>
       <c r="H537" t="s">
         <v>578</v>
       </c>
-      <c r="I537" t="s">
-        <v>579</v>
-      </c>
-      <c r="J537" t="s">
-        <v>578</v>
-      </c>
-      <c r="K537" t="s">
-        <v>578</v>
-      </c>
       <c r="M537" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="538" spans="1:14" x14ac:dyDescent="0.4">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="538" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A538" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B538" t="s">
         <v>541</v>
       </c>
+      <c r="D538" t="s">
+        <v>579</v>
+      </c>
+      <c r="E538" t="s">
+        <v>579</v>
+      </c>
+      <c r="F538" t="s">
+        <v>578</v>
+      </c>
+      <c r="G538" t="s">
+        <v>579</v>
+      </c>
       <c r="H538" t="s">
         <v>578</v>
       </c>
+      <c r="I538" t="s">
+        <v>579</v>
+      </c>
+      <c r="J538" t="s">
+        <v>578</v>
+      </c>
+      <c r="K538" t="s">
+        <v>578</v>
+      </c>
       <c r="M538" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="539" spans="1:14" x14ac:dyDescent="0.4">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="539" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A539" t="s">
+        <v>519</v>
+      </c>
+      <c r="B539" t="s">
+        <v>541</v>
+      </c>
+      <c r="H539" t="s">
+        <v>578</v>
+      </c>
+      <c r="M539" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="540" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A540" t="s">
         <v>520</v>
-      </c>
-      <c r="B539" t="s">
-        <v>543</v>
-      </c>
-      <c r="D539" t="s">
-        <v>579</v>
-      </c>
-      <c r="E539" t="s">
-        <v>579</v>
-      </c>
-      <c r="F539" t="s">
-        <v>579</v>
-      </c>
-      <c r="G539" t="s">
-        <v>579</v>
-      </c>
-      <c r="H539" t="s">
-        <v>579</v>
-      </c>
-      <c r="I539" t="s">
-        <v>579</v>
-      </c>
-      <c r="J539" t="s">
-        <v>578</v>
-      </c>
-      <c r="K539" t="s">
-        <v>579</v>
-      </c>
-      <c r="M539" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="540" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A540" t="s">
-        <v>521</v>
       </c>
       <c r="B540" t="s">
         <v>543</v>
@@ -11437,9 +11498,9 @@
         <v>579</v>
       </c>
     </row>
-    <row r="541" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="541" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A541" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B541" t="s">
         <v>543</v>
@@ -11460,10 +11521,10 @@
         <v>579</v>
       </c>
       <c r="I541" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="J541" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="K541" t="s">
         <v>579</v>
@@ -11472,9 +11533,9 @@
         <v>579</v>
       </c>
     </row>
-    <row r="542" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="542" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A542" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B542" t="s">
         <v>543</v>
@@ -11507,9 +11568,9 @@
         <v>579</v>
       </c>
     </row>
-    <row r="543" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="543" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A543" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B543" t="s">
         <v>543</v>
@@ -11530,10 +11591,10 @@
         <v>579</v>
       </c>
       <c r="I543" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="J543" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="K543" t="s">
         <v>579</v>
@@ -11542,55 +11603,55 @@
         <v>579</v>
       </c>
     </row>
-    <row r="544" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="544" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A544" t="s">
-        <v>627</v>
+        <v>524</v>
       </c>
       <c r="B544" t="s">
         <v>543</v>
       </c>
+      <c r="D544" t="s">
+        <v>579</v>
+      </c>
+      <c r="E544" t="s">
+        <v>579</v>
+      </c>
+      <c r="F544" t="s">
+        <v>579</v>
+      </c>
+      <c r="G544" t="s">
+        <v>579</v>
+      </c>
+      <c r="H544" t="s">
+        <v>579</v>
+      </c>
+      <c r="I544" t="s">
+        <v>579</v>
+      </c>
+      <c r="J544" t="s">
+        <v>578</v>
+      </c>
+      <c r="K544" t="s">
+        <v>579</v>
+      </c>
       <c r="M544" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="545" spans="1:14" x14ac:dyDescent="0.4">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="545" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A545" t="s">
-        <v>525</v>
+        <v>627</v>
       </c>
       <c r="B545" t="s">
         <v>543</v>
       </c>
-      <c r="D545" t="s">
-        <v>579</v>
-      </c>
-      <c r="E545" t="s">
-        <v>579</v>
-      </c>
-      <c r="F545" t="s">
-        <v>579</v>
-      </c>
-      <c r="G545" t="s">
-        <v>579</v>
-      </c>
-      <c r="H545" t="s">
-        <v>579</v>
-      </c>
-      <c r="I545" t="s">
-        <v>579</v>
-      </c>
-      <c r="J545" t="s">
-        <v>578</v>
-      </c>
-      <c r="K545" t="s">
-        <v>579</v>
-      </c>
       <c r="M545" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="546" spans="1:14" x14ac:dyDescent="0.4">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="546" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A546" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B546" t="s">
         <v>543</v>
@@ -11614,7 +11675,7 @@
         <v>579</v>
       </c>
       <c r="J546" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="K546" t="s">
         <v>579</v>
@@ -11622,13 +11683,10 @@
       <c r="M546" t="s">
         <v>579</v>
       </c>
-      <c r="N546" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="547" spans="1:14" x14ac:dyDescent="0.4">
+    </row>
+    <row r="547" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A547" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B547" t="s">
         <v>543</v>
@@ -11640,13 +11698,13 @@
         <v>579</v>
       </c>
       <c r="F547" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="G547" t="s">
         <v>579</v>
       </c>
       <c r="H547" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="I547" t="s">
         <v>579</v>
@@ -11658,12 +11716,15 @@
         <v>579</v>
       </c>
       <c r="M547" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="548" spans="1:14" x14ac:dyDescent="0.4">
+        <v>579</v>
+      </c>
+      <c r="O547" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="548" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A548" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B548" t="s">
         <v>543</v>
@@ -11695,48 +11756,27 @@
       <c r="M548" t="s">
         <v>578</v>
       </c>
-    </row>
-    <row r="549" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="N548" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="549" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A549" t="s">
-        <v>529</v>
+        <v>646</v>
       </c>
       <c r="B549" t="s">
         <v>543</v>
       </c>
-      <c r="D549" t="s">
-        <v>579</v>
-      </c>
-      <c r="E549" t="s">
-        <v>579</v>
-      </c>
-      <c r="F549" t="s">
-        <v>579</v>
-      </c>
-      <c r="G549" t="s">
-        <v>579</v>
-      </c>
-      <c r="H549" t="s">
-        <v>579</v>
-      </c>
-      <c r="I549" t="s">
-        <v>579</v>
-      </c>
-      <c r="J549" t="s">
-        <v>578</v>
-      </c>
-      <c r="K549" t="s">
-        <v>579</v>
-      </c>
-      <c r="M549" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="550" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="N549" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="550" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A550" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="B550" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="D550" t="s">
         <v>579</v>
@@ -11745,65 +11785,41 @@
         <v>579</v>
       </c>
       <c r="F550" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="G550" t="s">
         <v>579</v>
       </c>
       <c r="H550" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="I550" t="s">
         <v>579</v>
       </c>
       <c r="J550" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="K550" t="s">
         <v>579</v>
       </c>
       <c r="M550" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="551" spans="1:14" x14ac:dyDescent="0.4">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="551" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A551" t="s">
-        <v>531</v>
+        <v>647</v>
       </c>
       <c r="B551" t="s">
-        <v>541</v>
-      </c>
-      <c r="D551" t="s">
-        <v>579</v>
-      </c>
-      <c r="E551" t="s">
-        <v>579</v>
-      </c>
-      <c r="F551" t="s">
-        <v>579</v>
-      </c>
-      <c r="G551" t="s">
-        <v>579</v>
-      </c>
-      <c r="H551" t="s">
-        <v>579</v>
-      </c>
-      <c r="I551" t="s">
-        <v>579</v>
-      </c>
-      <c r="J551" t="s">
-        <v>578</v>
-      </c>
-      <c r="K551" t="s">
-        <v>579</v>
-      </c>
-      <c r="M551" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="552" spans="1:14" x14ac:dyDescent="0.4">
+        <v>543</v>
+      </c>
+      <c r="N551" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="552" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A552" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="B552" t="s">
         <v>543</v>
@@ -11824,10 +11840,10 @@
         <v>579</v>
       </c>
       <c r="I552" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="J552" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="K552" t="s">
         <v>579</v>
@@ -11836,47 +11852,23 @@
         <v>579</v>
       </c>
     </row>
-    <row r="553" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="553" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A553" t="s">
-        <v>533</v>
+        <v>648</v>
       </c>
       <c r="B553" t="s">
         <v>543</v>
       </c>
-      <c r="D553" t="s">
-        <v>579</v>
-      </c>
-      <c r="E553" t="s">
-        <v>579</v>
-      </c>
-      <c r="F553" t="s">
-        <v>579</v>
-      </c>
-      <c r="G553" t="s">
-        <v>579</v>
-      </c>
-      <c r="H553" t="s">
-        <v>579</v>
-      </c>
-      <c r="I553" t="s">
-        <v>579</v>
-      </c>
-      <c r="J553" t="s">
-        <v>578</v>
-      </c>
-      <c r="K553" t="s">
-        <v>579</v>
-      </c>
-      <c r="M553" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="554" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="N553" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="554" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A554" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="B554" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="D554" t="s">
         <v>579</v>
@@ -11906,12 +11898,12 @@
         <v>579</v>
       </c>
     </row>
-    <row r="555" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="555" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A555" t="s">
-        <v>594</v>
+        <v>531</v>
       </c>
       <c r="B555" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="D555" t="s">
         <v>579</v>
@@ -11941,65 +11933,149 @@
         <v>579</v>
       </c>
     </row>
-    <row r="556" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="556" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A556" t="s">
-        <v>628</v>
+        <v>532</v>
       </c>
       <c r="B556" t="s">
         <v>543</v>
       </c>
+      <c r="D556" t="s">
+        <v>579</v>
+      </c>
+      <c r="E556" t="s">
+        <v>579</v>
+      </c>
+      <c r="F556" t="s">
+        <v>579</v>
+      </c>
+      <c r="G556" t="s">
+        <v>579</v>
+      </c>
+      <c r="H556" t="s">
+        <v>579</v>
+      </c>
+      <c r="I556" t="s">
+        <v>578</v>
+      </c>
+      <c r="J556" t="s">
+        <v>579</v>
+      </c>
+      <c r="K556" t="s">
+        <v>579</v>
+      </c>
       <c r="M556" t="s">
         <v>579</v>
       </c>
-      <c r="N556" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="557" spans="1:14" x14ac:dyDescent="0.4">
+    </row>
+    <row r="557" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A557" t="s">
-        <v>596</v>
+        <v>533</v>
       </c>
       <c r="B557" t="s">
         <v>543</v>
       </c>
+      <c r="D557" t="s">
+        <v>579</v>
+      </c>
+      <c r="E557" t="s">
+        <v>579</v>
+      </c>
+      <c r="F557" t="s">
+        <v>579</v>
+      </c>
+      <c r="G557" t="s">
+        <v>579</v>
+      </c>
+      <c r="H557" t="s">
+        <v>579</v>
+      </c>
+      <c r="I557" t="s">
+        <v>579</v>
+      </c>
       <c r="J557" t="s">
         <v>578</v>
       </c>
+      <c r="K557" t="s">
+        <v>579</v>
+      </c>
       <c r="M557" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="558" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="558" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A558" t="s">
-        <v>629</v>
+        <v>534</v>
       </c>
       <c r="B558" t="s">
-        <v>541</v>
+        <v>543</v>
+      </c>
+      <c r="D558" t="s">
+        <v>579</v>
+      </c>
+      <c r="E558" t="s">
+        <v>579</v>
+      </c>
+      <c r="F558" t="s">
+        <v>579</v>
+      </c>
+      <c r="G558" t="s">
+        <v>579</v>
+      </c>
+      <c r="H558" t="s">
+        <v>579</v>
+      </c>
+      <c r="I558" t="s">
+        <v>579</v>
+      </c>
+      <c r="J558" t="s">
+        <v>578</v>
+      </c>
+      <c r="K558" t="s">
+        <v>579</v>
       </c>
       <c r="M558" t="s">
         <v>579</v>
       </c>
-      <c r="N558" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="559" spans="1:14" x14ac:dyDescent="0.4">
+    </row>
+    <row r="559" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A559" t="s">
-        <v>630</v>
+        <v>594</v>
       </c>
       <c r="B559" t="s">
         <v>543</v>
       </c>
+      <c r="D559" t="s">
+        <v>579</v>
+      </c>
+      <c r="E559" t="s">
+        <v>579</v>
+      </c>
+      <c r="F559" t="s">
+        <v>579</v>
+      </c>
+      <c r="G559" t="s">
+        <v>579</v>
+      </c>
+      <c r="H559" t="s">
+        <v>579</v>
+      </c>
+      <c r="I559" t="s">
+        <v>579</v>
+      </c>
+      <c r="J559" t="s">
+        <v>578</v>
+      </c>
+      <c r="K559" t="s">
+        <v>579</v>
+      </c>
       <c r="M559" t="s">
         <v>579</v>
       </c>
-      <c r="N559" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="560" spans="1:14" x14ac:dyDescent="0.4">
+    </row>
+    <row r="560" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A560" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="B560" t="s">
         <v>543</v>
@@ -12010,13 +12086,16 @@
       <c r="N560" t="s">
         <v>578</v>
       </c>
-    </row>
-    <row r="561" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="O560" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="561" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A561" t="s">
-        <v>632</v>
+        <v>596</v>
       </c>
       <c r="B561" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="J561" t="s">
         <v>578</v>
@@ -12025,96 +12104,162 @@
         <v>579</v>
       </c>
     </row>
-    <row r="562" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="562" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A562" t="s">
-        <v>597</v>
+        <v>649</v>
       </c>
       <c r="B562" t="s">
+        <v>650</v>
+      </c>
+      <c r="N562" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="563" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A563" t="s">
+        <v>629</v>
+      </c>
+      <c r="B563" t="s">
         <v>541</v>
       </c>
-      <c r="M562" t="s">
-        <v>579</v>
-      </c>
-      <c r="N562" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="563" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A563" t="s">
-        <v>633</v>
-      </c>
-      <c r="B563" t="s">
-        <v>543</v>
-      </c>
-      <c r="J563" t="s">
-        <v>578</v>
-      </c>
       <c r="M563" t="s">
         <v>579</v>
       </c>
-    </row>
-    <row r="564" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="O563" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="564" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A564" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="B564" t="s">
         <v>543</v>
       </c>
-      <c r="J564" t="s">
-        <v>578</v>
-      </c>
       <c r="M564" t="s">
         <v>579</v>
       </c>
-    </row>
-    <row r="565" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="O564" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="565" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A565" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="B565" t="s">
         <v>543</v>
       </c>
-      <c r="J565" t="s">
-        <v>578</v>
-      </c>
       <c r="M565" t="s">
         <v>579</v>
       </c>
-    </row>
-    <row r="566" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="N565" t="s">
+        <v>578</v>
+      </c>
+      <c r="O565" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="566" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A566" t="s">
+        <v>632</v>
+      </c>
+      <c r="B566" t="s">
+        <v>539</v>
+      </c>
+      <c r="J566" t="s">
+        <v>578</v>
+      </c>
+      <c r="M566" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="567" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A567" t="s">
+        <v>597</v>
+      </c>
+      <c r="B567" t="s">
+        <v>541</v>
+      </c>
+      <c r="M567" t="s">
+        <v>579</v>
+      </c>
+      <c r="O567" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="568" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A568" t="s">
+        <v>633</v>
+      </c>
+      <c r="B568" t="s">
+        <v>543</v>
+      </c>
+      <c r="J568" t="s">
+        <v>578</v>
+      </c>
+      <c r="M568" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="569" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A569" t="s">
+        <v>634</v>
+      </c>
+      <c r="B569" t="s">
+        <v>543</v>
+      </c>
+      <c r="J569" t="s">
+        <v>578</v>
+      </c>
+      <c r="M569" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="570" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A570" t="s">
+        <v>635</v>
+      </c>
+      <c r="B570" t="s">
+        <v>543</v>
+      </c>
+      <c r="J570" t="s">
+        <v>578</v>
+      </c>
+      <c r="M570" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="571" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A571" t="s">
         <v>636</v>
       </c>
-      <c r="B566" t="s">
+      <c r="B571" t="s">
         <v>543</v>
       </c>
-      <c r="J566" t="s">
-        <v>578</v>
-      </c>
-      <c r="M566" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="567" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="A567" t="s">
+      <c r="J571" t="s">
+        <v>578</v>
+      </c>
+      <c r="M571" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="572" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="A572" t="s">
         <v>637</v>
       </c>
-      <c r="B567" t="s">
+      <c r="B572" t="s">
         <v>543</v>
       </c>
-      <c r="J567" t="s">
-        <v>578</v>
-      </c>
-      <c r="M567" t="s">
+      <c r="J572" t="s">
+        <v>578</v>
+      </c>
+      <c r="M572" t="s">
         <v>579</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N555" xr:uid="{00E93854-CA35-4A6A-8541-6A17C44224E7}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N555">
-      <sortCondition ref="A1:A555"/>
-    </sortState>
-  </autoFilter>
+  <autoFilter ref="A1:O572" xr:uid="{00E93854-CA35-4A6A-8541-6A17C44224E7}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="A448:A455">
     <cfRule type="duplicateValues" dxfId="4" priority="6"/>
@@ -12128,7 +12273,7 @@
   <conditionalFormatting sqref="A551:A555">
     <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A568:A642 A456:A548 A556:A561">
+  <conditionalFormatting sqref="A569:A643 A456:A548 A556:A562">
     <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
